--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Name</t>
   </si>
@@ -35,6 +35,54 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>Rayan Irfan</t>
+  </si>
+  <si>
+    <t>US History I H</t>
+  </si>
+  <si>
+    <t>Chemistry H</t>
+  </si>
+  <si>
+    <t>German III H</t>
+  </si>
+  <si>
+    <t>Algebra II H</t>
+  </si>
+  <si>
+    <t>English 10 H</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>US History 1 H</t>
+  </si>
+  <si>
+    <t>Algebra II Honors</t>
+  </si>
+  <si>
+    <t>Anish Setty</t>
+  </si>
+  <si>
+    <t>French III H</t>
+  </si>
+  <si>
+    <t>Shiv Patel</t>
+  </si>
+  <si>
+    <t>Spanish III H</t>
+  </si>
+  <si>
+    <t>Nathan Son</t>
+  </si>
+  <si>
+    <t>Guitar I</t>
+  </si>
+  <si>
+    <t>Symphony Orchestra S</t>
   </si>
 </sst>
 </file>
@@ -321,11 +369,112 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="15.75" customHeight="1"/>
-    <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1"/>
